--- a/data/employees/EMP098/AST-EMP098-06.xlsx
+++ b/data/employees/EMP098/AST-EMP098-06.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skills Matrix" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,36 +26,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E4057"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00048A81"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -69,17 +47,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,215 +414,1883 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Skills Matrix - Jamie Brown (HR)</t>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>EmployeeId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Narrative</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Author: Jamie Brown | Role: Manager | Location: Hsinchu | Date: 2025-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EMP098</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ast Emp098 06</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-W01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>75</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP098 contributes to ast emp098 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EMP098</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ast Emp098 06</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-W02</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>62</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP098 contributes to ast emp098 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Employee ID</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Department</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Role</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Skills</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Last Review Date</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Rating</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EMP098</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ast Emp098 06</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-W03</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>67</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP098 contributes to ast emp098 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>EMP006</t>
+          <t>EMP098</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Avery Wilson</t>
+          <t>Ast Emp098 06</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>2026-W04</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Specialist</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Azure AI, Fabric</t>
-        </is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>95</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>4.2</v>
+          <t>Section 1: Data quality remediation. EMP098 contributes to ast emp098 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EMP011</t>
+          <t>EMP098</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Alex Garcia</t>
+          <t>Ast Emp098 06</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>2026-W05</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Lead</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Synapse, TypeScript</t>
-        </is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>65</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>3.9</v>
+          <t>Section 1: Knowledge transfer and onboarding. EMP098 contributes to ast emp098 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EMP016</t>
+          <t>EMP098</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Avery Wilson</t>
+          <t>Ast Emp098 06</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>2026-W06</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Engineer</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Python, SQL</t>
-        </is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>94</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>4.5</v>
+          <t>Section 1: Fabric semantic model planning. EMP098 contributes to ast emp098 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EMP021</t>
+          <t>EMP098</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Alex Garcia</t>
+          <t>Ast Emp098 06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>2026-W07</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>96</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP098 contributes to ast emp098 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EMP098</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ast Emp098 06</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-W08</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>72</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP098 contributes to ast emp098 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EMP098</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ast Emp098 06</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-W09</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>91</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP098 contributes to ast emp098 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EMP098</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ast Emp098 06</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>71</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP098 contributes to ast emp098 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EMP098</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ast Emp098 06</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>88</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP098 contributes to ast emp098 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EMP098</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ast Emp098 06</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>79</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP098 contributes to ast emp098 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EMP098</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ast Emp098 06</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>73</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP098 contributes to ast emp098 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EMP098</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ast Emp098 06</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>88</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP098 contributes to ast emp098 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EMP098</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ast Emp098 06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>81</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP098 contributes to ast emp098 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EMP098</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ast Emp098 06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>75</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP098 contributes to ast emp098 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EMP098</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ast Emp098 06</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>96</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP098 contributes to ast emp098 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>EMP098</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ast Emp098 06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-W18</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>66</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP098 contributes to ast emp098 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EMP098</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ast Emp098 06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-W19</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>86</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP098 contributes to ast emp098 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EMP098</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ast Emp098 06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-W20</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>82</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP098 contributes to ast emp098 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EMP098</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ast Emp098 06</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-W21</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>87</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP098 contributes to ast emp098 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EMP098</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ast Emp098 06</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-W22</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>87</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP098 contributes to ast emp098 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EMP098</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ast Emp098 06</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-W23</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>80</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP098 contributes to ast emp098 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EMP098</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ast Emp098 06</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>90</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP098 contributes to ast emp098 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EMP098</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP098 contributes to ast emp098 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EMP098</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP098 contributes to ast emp098 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EMP098</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP098 contributes to ast emp098 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EMP098</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP098 contributes to ast emp098 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EMP098</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP098 contributes to ast emp098 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EMP098</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP098 contributes to ast emp098 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>EMP098</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ontology, MLOps</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>4</v>
+          <t>Section 1: Operational risk review. EMP098 contributes to ast emp098 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EMP098</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP098 contributes to ast emp098 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EMP098</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP098 contributes to ast emp098 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>EMP098</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP098 contributes to ast emp098 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EMP098</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP098 contributes to ast emp098 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EMP098</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP098 contributes to ast emp098 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>EMP098</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP098 contributes to ast emp098 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EMP098</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP098 contributes to ast emp098 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EMP098</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP098 contributes to ast emp098 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>EMP098</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP098 contributes to ast emp098 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>EMP098</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP098 contributes to ast emp098 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>EMP098</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP098 contributes to ast emp098 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>EMP098</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP098 contributes to ast emp098 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>EMP098</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP098 contributes to ast emp098 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>EMP098</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP098 contributes to ast emp098 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EMP098</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP098 contributes to ast emp098 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EMP098</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP098 contributes to ast emp098 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>EMP098</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP098 contributes to ast emp098 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>EMP098</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP098 contributes to ast emp098 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>EMP098</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP098 contributes to ast emp098 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>EMP098</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP098 contributes to ast emp098 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EMP098</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP098 contributes to ast emp098 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>EMP098</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP098 contributes to ast emp098 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>EMP098</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP098 contributes to ast emp098 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>EMP098</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP098 contributes to ast emp098 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>EMP098</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP098 contributes to ast emp098 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>EMP098</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP098 contributes to ast emp098 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>EMP098</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP098 contributes to ast emp098 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>EMP098</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP098 contributes to ast emp098 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>EMP098</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP098 contributes to ast emp098 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EMP098</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP098 contributes to ast emp098 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EMP098</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP098 contributes to ast emp098 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>EMP098</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP098 contributes to ast emp098 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>EMP098</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP098 contributes to ast emp098 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>